--- a/КОНТАКТЫ ПОДРАЗДЕЛЕНИЯ.xlsx
+++ b/КОНТАКТЫ ПОДРАЗДЕЛЕНИЯ.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="551">
   <si>
     <t xml:space="preserve">Подразделение</t>
   </si>
@@ -331,6 +331,9 @@
     <t xml:space="preserve">8-904-557-28-57</t>
   </si>
   <si>
+    <t xml:space="preserve">Макаров</t>
+  </si>
+  <si>
     <t xml:space="preserve">Типунина Марина Николаевна</t>
   </si>
   <si>
@@ -1667,6 +1670,9 @@
   </si>
   <si>
     <t xml:space="preserve">+7 (911)834-07-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маль</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +1688,6 @@
       <sz val="8"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1703,34 +1708,29 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFCCCCCC"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFCCCCCC"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1738,28 +1738,24 @@
       <color rgb="FF00A933"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF00A933"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFB2B2B2"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFB2B2B2"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1993,13 +1989,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr defaultColWidth="10.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="41.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="65.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="25.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="17.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="10.5"/>
   </cols>
   <sheetData>
@@ -2107,6 +2103,9 @@
       <c r="D9" s="10" t="s">
         <v>19</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="n">
@@ -2121,6 +2120,9 @@
       <c r="D10" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="n">
@@ -2135,6 +2137,9 @@
       <c r="D11" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
@@ -2163,6 +2168,9 @@
       <c r="D13" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="n">
@@ -2190,6 +2198,9 @@
       </c>
       <c r="D15" s="10" t="s">
         <v>37</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2551,19 +2562,25 @@
       <c r="D42" s="10" t="s">
         <v>102</v>
       </c>
+      <c r="E42" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="n">
         <v>11</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>101</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2571,13 +2588,13 @@
         <v>12</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2585,13 +2602,13 @@
         <v>13</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2599,13 +2616,13 @@
         <v>14</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2613,13 +2630,13 @@
         <v>15</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2627,13 +2644,13 @@
         <v>16</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2641,13 +2658,13 @@
         <v>17</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2655,13 +2672,13 @@
         <v>18</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>91</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2669,13 +2686,13 @@
         <v>19</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>91</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2683,13 +2700,13 @@
         <v>20</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2697,13 +2714,13 @@
         <v>21</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2711,13 +2728,13 @@
         <v>22</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2725,18 +2742,18 @@
         <v>23</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2748,13 +2765,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2762,13 +2779,13 @@
         <v>2</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2776,13 +2793,13 @@
         <v>3</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2790,13 +2807,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2804,13 +2821,13 @@
         <v>5</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,13 +2835,13 @@
         <v>6</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,18 +2849,18 @@
         <v>7</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2855,13 +2872,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2869,13 +2886,13 @@
         <v>2</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2883,13 +2900,13 @@
         <v>3</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2897,13 +2914,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2911,18 +2928,18 @@
         <v>5</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -2934,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2948,18 +2965,18 @@
         <v>2</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2971,13 +2988,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E74" s="18" t="n">
         <v>1</v>
@@ -2988,13 +3005,13 @@
         <v>2</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3002,13 +3019,13 @@
         <v>3</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3016,13 +3033,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3030,18 +3047,18 @@
         <v>5</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -3053,13 +3070,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E80" s="22"/>
     </row>
@@ -3068,13 +3085,13 @@
         <v>2</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3082,13 +3099,13 @@
         <v>3</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3096,13 +3113,13 @@
         <v>4</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3110,13 +3127,13 @@
         <v>5</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3124,13 +3141,13 @@
         <v>6</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3138,13 +3155,13 @@
         <v>7</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3152,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3166,13 +3183,13 @@
         <v>9</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3180,13 +3197,13 @@
         <v>10</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3194,18 +3211,18 @@
         <v>11</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -3217,18 +3234,18 @@
         <v>1</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3240,13 +3257,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3254,13 +3271,13 @@
         <v>2</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3268,13 +3285,13 @@
         <v>3</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3282,13 +3299,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3296,13 +3313,13 @@
         <v>5</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3310,13 +3327,13 @@
         <v>6</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3324,18 +3341,18 @@
         <v>7</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -3347,13 +3364,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3361,18 +3378,18 @@
         <v>2</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -3384,13 +3401,13 @@
         <v>1</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,13 +3415,13 @@
         <v>2</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,13 +3429,13 @@
         <v>3</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3426,18 +3443,18 @@
         <v>4</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -3449,13 +3466,13 @@
         <v>1</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,13 +3480,13 @@
         <v>2</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3477,13 +3494,13 @@
         <v>3</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3491,18 +3508,18 @@
         <v>4</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -3514,13 +3531,13 @@
         <v>1</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3528,13 +3545,13 @@
         <v>2</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3542,13 +3559,13 @@
         <v>3</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3556,13 +3573,13 @@
         <v>4</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3570,13 +3587,13 @@
         <v>5</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3584,13 +3601,13 @@
         <v>6</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3598,13 +3615,13 @@
         <v>7</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3612,13 +3629,13 @@
         <v>8</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3626,13 +3643,13 @@
         <v>9</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3640,18 +3657,18 @@
         <v>10</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -3663,13 +3680,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3677,13 +3694,13 @@
         <v>2</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3691,13 +3708,13 @@
         <v>3</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3705,13 +3722,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3719,32 +3736,32 @@
         <v>5</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="9" t="n">
         <v>6</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="132" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -3756,13 +3773,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3770,13 +3787,13 @@
         <v>2</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3784,13 +3801,13 @@
         <v>3</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3798,13 +3815,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3812,13 +3829,13 @@
         <v>5</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3826,18 +3843,18 @@
         <v>6</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="139" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -3849,13 +3866,13 @@
         <v>1</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3863,13 +3880,13 @@
         <v>2</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3877,13 +3894,13 @@
         <v>3</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,13 +3908,13 @@
         <v>4</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3905,13 +3922,13 @@
         <v>5</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3919,13 +3936,13 @@
         <v>6</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3933,13 +3950,13 @@
         <v>7</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3947,18 +3964,18 @@
         <v>8</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="148" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -3970,13 +3987,13 @@
         <v>1</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3984,13 +4001,13 @@
         <v>2</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,13 +4015,13 @@
         <v>3</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4012,10 +4029,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D152" s="10"/>
     </row>
@@ -4024,18 +4041,18 @@
         <v>5</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="154" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -4047,18 +4064,18 @@
         <v>1</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="156" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -4070,13 +4087,13 @@
         <v>1</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4084,13 +4101,13 @@
         <v>2</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4098,18 +4115,18 @@
         <v>3</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="160" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -4121,13 +4138,13 @@
         <v>1</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4135,13 +4152,13 @@
         <v>2</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4149,18 +4166,18 @@
         <v>3</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="164" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -4172,13 +4189,13 @@
         <v>1</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4186,13 +4203,13 @@
         <v>2</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,13 +4217,13 @@
         <v>3</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4214,13 +4231,13 @@
         <v>4</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4228,13 +4245,13 @@
         <v>5</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4242,13 +4259,13 @@
         <v>6</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4256,13 +4273,13 @@
         <v>7</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4270,13 +4287,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4284,13 +4301,13 @@
         <v>9</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4298,13 +4315,13 @@
         <v>10</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>77</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4312,13 +4329,13 @@
         <v>11</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4326,13 +4343,13 @@
         <v>12</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4340,18 +4357,18 @@
         <v>13</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -4363,13 +4380,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4377,13 +4394,13 @@
         <v>2</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4391,18 +4408,18 @@
         <v>3</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="182" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -4414,13 +4431,13 @@
         <v>1</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D183" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4428,13 +4445,13 @@
         <v>2</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4442,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,18 +4473,18 @@
         <v>4</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="187" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -4479,13 +4496,13 @@
         <v>1</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4493,13 +4510,13 @@
         <v>2</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4507,13 +4524,13 @@
         <v>3</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4521,13 +4538,13 @@
         <v>4</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4535,13 +4552,13 @@
         <v>5</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4549,18 +4566,18 @@
         <v>6</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -4572,13 +4589,13 @@
         <v>1</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4586,13 +4603,13 @@
         <v>2</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4600,13 +4617,13 @@
         <v>3</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D197" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4614,13 +4631,13 @@
         <v>4</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D198" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4628,13 +4645,13 @@
         <v>5</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D199" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,13 +4659,13 @@
         <v>6</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4656,13 +4673,13 @@
         <v>7</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4670,13 +4687,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4684,13 +4701,13 @@
         <v>9</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4698,13 +4715,13 @@
         <v>10</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4712,13 +4729,13 @@
         <v>11</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4726,13 +4743,13 @@
         <v>12</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4740,13 +4757,13 @@
         <v>13</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D207" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4754,13 +4771,13 @@
         <v>14</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D208" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4768,13 +4785,13 @@
         <v>15</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D209" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4782,13 +4799,13 @@
         <v>16</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D210" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4796,18 +4813,18 @@
         <v>17</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D211" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="212" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
@@ -4819,50 +4836,50 @@
         <v>1</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D213" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
       <c r="E214" s="7"/>
     </row>
-    <row r="215" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D215" s="10" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D216" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4870,27 +4887,27 @@
         <v>3</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D217" s="10" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="9" t="n">
         <v>4</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D218" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4898,13 +4915,13 @@
         <v>5</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D219" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4912,18 +4929,18 @@
         <v>6</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B221" s="6"/>
       <c r="C221" s="6"/>
@@ -4935,18 +4952,18 @@
         <v>1</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D222" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B223" s="6"/>
       <c r="C223" s="6"/>
@@ -4958,13 +4975,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D224" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4972,13 +4989,13 @@
         <v>2</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4986,18 +5003,18 @@
         <v>3</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="227" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B227" s="6"/>
       <c r="C227" s="6"/>
@@ -5009,13 +5026,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5023,18 +5040,23 @@
         <v>2</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D229" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="230" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1"/>
       <c r="E230" s="3"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="2" t="s">
+        <v>550</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="33">
